--- a/sulamericana/datasets_sula/1_resultados_oitavas_sula.xlsx
+++ b/sulamericana/datasets_sula/1_resultados_oitavas_sula.xlsx
@@ -496,13 +496,13 @@
         <v>14</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>104.97</v>
       </c>
       <c r="E2" t="s">
         <v>22</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>97.56999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -516,13 +516,13 @@
         <v>15</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>114.97</v>
       </c>
       <c r="E3" t="s">
         <v>23</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>104.38</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -536,13 +536,13 @@
         <v>16</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>111.47</v>
       </c>
       <c r="E4" t="s">
         <v>24</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>115.35</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -556,13 +556,13 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>101.87</v>
       </c>
       <c r="E5" t="s">
         <v>25</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>95.37</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -576,13 +576,13 @@
         <v>18</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>117.22</v>
       </c>
       <c r="E6" t="s">
         <v>26</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>97.62</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -596,13 +596,13 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>84.06999999999999</v>
       </c>
       <c r="E7" t="s">
         <v>27</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>95.02</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -616,13 +616,13 @@
         <v>20</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>102.32</v>
       </c>
       <c r="E8" t="s">
         <v>28</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>112.02</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -636,13 +636,13 @@
         <v>21</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>95.62</v>
       </c>
       <c r="E9" t="s">
         <v>29</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>114.42</v>
       </c>
     </row>
   </sheetData>
@@ -685,14 +685,8 @@
       <c r="C2" t="s">
         <v>22</v>
       </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
       <c r="E2" t="s">
         <v>14</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -705,14 +699,8 @@
       <c r="C3" t="s">
         <v>23</v>
       </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
       <c r="E3" t="s">
         <v>15</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -725,14 +713,8 @@
       <c r="C4" t="s">
         <v>24</v>
       </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
       <c r="E4" t="s">
         <v>16</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -745,14 +727,8 @@
       <c r="C5" t="s">
         <v>25</v>
       </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
       <c r="E5" t="s">
         <v>17</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -765,14 +741,8 @@
       <c r="C6" t="s">
         <v>26</v>
       </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
       <c r="E6" t="s">
         <v>18</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -785,14 +755,8 @@
       <c r="C7" t="s">
         <v>27</v>
       </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
       <c r="E7" t="s">
         <v>19</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -805,15 +769,9 @@
       <c r="C8" t="s">
         <v>28</v>
       </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
       <c r="E8" t="s">
         <v>20</v>
       </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
@@ -825,14 +783,8 @@
       <c r="C9" t="s">
         <v>29</v>
       </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
       <c r="E9" t="s">
         <v>21</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/sulamericana/datasets_sula/1_resultados_oitavas_sula.xlsx
+++ b/sulamericana/datasets_sula/1_resultados_oitavas_sula.xlsx
@@ -496,13 +496,13 @@
         <v>14</v>
       </c>
       <c r="D2">
-        <v>104.97</v>
+        <v>117.04</v>
       </c>
       <c r="E2" t="s">
         <v>22</v>
       </c>
       <c r="F2">
-        <v>97.56999999999999</v>
+        <v>97.64</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -516,13 +516,13 @@
         <v>15</v>
       </c>
       <c r="D3">
-        <v>114.97</v>
+        <v>123.04</v>
       </c>
       <c r="E3" t="s">
         <v>23</v>
       </c>
       <c r="F3">
-        <v>104.38</v>
+        <v>104.29</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -536,13 +536,13 @@
         <v>16</v>
       </c>
       <c r="D4">
-        <v>111.47</v>
+        <v>119.54</v>
       </c>
       <c r="E4" t="s">
         <v>24</v>
       </c>
       <c r="F4">
-        <v>115.35</v>
+        <v>110.35</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -556,13 +556,13 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>101.87</v>
+        <v>103.07</v>
       </c>
       <c r="E5" t="s">
         <v>25</v>
       </c>
       <c r="F5">
-        <v>95.37</v>
+        <v>115.44</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -576,13 +576,13 @@
         <v>18</v>
       </c>
       <c r="D6">
-        <v>117.22</v>
+        <v>116.79</v>
       </c>
       <c r="E6" t="s">
         <v>26</v>
       </c>
       <c r="F6">
-        <v>97.62</v>
+        <v>106.39</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -596,13 +596,13 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>84.06999999999999</v>
+        <v>99.64</v>
       </c>
       <c r="E7" t="s">
         <v>27</v>
       </c>
       <c r="F7">
-        <v>95.02</v>
+        <v>104.29</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -616,13 +616,13 @@
         <v>20</v>
       </c>
       <c r="D8">
-        <v>102.32</v>
+        <v>103.59</v>
       </c>
       <c r="E8" t="s">
         <v>28</v>
       </c>
       <c r="F8">
-        <v>112.02</v>
+        <v>120.79</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -636,13 +636,13 @@
         <v>21</v>
       </c>
       <c r="D9">
-        <v>95.62</v>
+        <v>104.89</v>
       </c>
       <c r="E9" t="s">
         <v>29</v>
       </c>
       <c r="F9">
-        <v>114.42</v>
+        <v>122.49</v>
       </c>
     </row>
   </sheetData>

--- a/sulamericana/datasets_sula/1_resultados_oitavas_sula.xlsx
+++ b/sulamericana/datasets_sula/1_resultados_oitavas_sula.xlsx
@@ -496,13 +496,13 @@
         <v>14</v>
       </c>
       <c r="D2">
-        <v>117.04</v>
+        <v>117.0400390625</v>
       </c>
       <c r="E2" t="s">
         <v>22</v>
       </c>
       <c r="F2">
-        <v>97.64</v>
+        <v>97.64013671875</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -516,13 +516,13 @@
         <v>15</v>
       </c>
       <c r="D3">
-        <v>123.04</v>
+        <v>123.0400390625</v>
       </c>
       <c r="E3" t="s">
         <v>23</v>
       </c>
       <c r="F3">
-        <v>104.29</v>
+        <v>104.2900390625</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -536,13 +536,13 @@
         <v>16</v>
       </c>
       <c r="D4">
-        <v>119.54</v>
+        <v>119.5400390625</v>
       </c>
       <c r="E4" t="s">
         <v>24</v>
       </c>
       <c r="F4">
-        <v>110.35</v>
+        <v>110.35009765625</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -556,13 +556,13 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>103.07</v>
+        <v>103.06982421875</v>
       </c>
       <c r="E5" t="s">
         <v>25</v>
       </c>
       <c r="F5">
-        <v>115.44</v>
+        <v>115.43994140625</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -576,13 +576,13 @@
         <v>18</v>
       </c>
       <c r="D6">
-        <v>116.79</v>
+        <v>116.7900390625</v>
       </c>
       <c r="E6" t="s">
         <v>26</v>
       </c>
       <c r="F6">
-        <v>106.39</v>
+        <v>106.39013671875</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -596,13 +596,13 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>99.64</v>
+        <v>99.64013671875</v>
       </c>
       <c r="E7" t="s">
         <v>27</v>
       </c>
       <c r="F7">
-        <v>104.29</v>
+        <v>104.2900390625</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -616,13 +616,13 @@
         <v>20</v>
       </c>
       <c r="D8">
-        <v>103.59</v>
+        <v>103.58984375</v>
       </c>
       <c r="E8" t="s">
         <v>28</v>
       </c>
       <c r="F8">
-        <v>120.79</v>
+        <v>120.7900390625</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -636,13 +636,13 @@
         <v>21</v>
       </c>
       <c r="D9">
-        <v>104.89</v>
+        <v>104.89013671875</v>
       </c>
       <c r="E9" t="s">
         <v>29</v>
       </c>
       <c r="F9">
-        <v>122.49</v>
+        <v>122.490234375</v>
       </c>
     </row>
   </sheetData>

--- a/sulamericana/datasets_sula/1_resultados_oitavas_sula.xlsx
+++ b/sulamericana/datasets_sula/1_resultados_oitavas_sula.xlsx
@@ -685,8 +685,14 @@
       <c r="C2" t="s">
         <v>22</v>
       </c>
+      <c r="D2">
+        <v>77.580078125</v>
+      </c>
       <c r="E2" t="s">
         <v>14</v>
+      </c>
+      <c r="F2">
+        <v>77.85009765625</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -699,8 +705,14 @@
       <c r="C3" t="s">
         <v>23</v>
       </c>
+      <c r="D3">
+        <v>54.330078125</v>
+      </c>
       <c r="E3" t="s">
         <v>15</v>
+      </c>
+      <c r="F3">
+        <v>74.75</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -713,8 +725,14 @@
       <c r="C4" t="s">
         <v>24</v>
       </c>
+      <c r="D4">
+        <v>51.080078125</v>
+      </c>
       <c r="E4" t="s">
         <v>16</v>
+      </c>
+      <c r="F4">
+        <v>63.0400390625</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -727,8 +745,14 @@
       <c r="C5" t="s">
         <v>25</v>
       </c>
+      <c r="D5">
+        <v>57.72998046875</v>
+      </c>
       <c r="E5" t="s">
         <v>17</v>
+      </c>
+      <c r="F5">
+        <v>62.989990234375</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -741,8 +765,14 @@
       <c r="C6" t="s">
         <v>26</v>
       </c>
+      <c r="D6">
+        <v>53.780029296875</v>
+      </c>
       <c r="E6" t="s">
         <v>18</v>
+      </c>
+      <c r="F6">
+        <v>76.47998046875</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -755,8 +785,14 @@
       <c r="C7" t="s">
         <v>27</v>
       </c>
+      <c r="D7">
+        <v>48.080078125</v>
+      </c>
       <c r="E7" t="s">
         <v>19</v>
+      </c>
+      <c r="F7">
+        <v>75.8798828125</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -769,9 +805,15 @@
       <c r="C8" t="s">
         <v>28</v>
       </c>
+      <c r="D8">
+        <v>41.949951171875</v>
+      </c>
       <c r="E8" t="s">
         <v>20</v>
       </c>
+      <c r="F8">
+        <v>76.72998046875</v>
+      </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
@@ -783,8 +825,14 @@
       <c r="C9" t="s">
         <v>29</v>
       </c>
+      <c r="D9">
+        <v>53.47998046875</v>
+      </c>
       <c r="E9" t="s">
         <v>21</v>
+      </c>
+      <c r="F9">
+        <v>50.25</v>
       </c>
     </row>
   </sheetData>
